--- a/data/output/2025/evaluasi_15.xlsx
+++ b/data/output/2025/evaluasi_15.xlsx
@@ -1322,7 +1322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1382,6 +1382,146 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanjung Jabung Timur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>42.16948920097999</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanjung Jabung Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6.024819130315969</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanjung Jabung Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.28738455114109</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanjung Jabung Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.06430104590438991</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanjung Jabung Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.11791870609103</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1484,6 +1624,90 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1571</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Jambi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>13.44089556187406</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1571</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Jambi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4782914169878251</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1571</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Jambi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3220274647107719</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1558,6 +1782,62 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1572</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Sungai Penuh</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-4.863500350409669</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1572</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Sungai Penuh</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.2597098123165122</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1744,6 +2024,146 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kerinci</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.725654628302158</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kerinci</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.656706464912675</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kerinci</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.3973267534910622</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kerinci</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.761547398329984</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kerinci</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3505210917332733</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1758,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1972,18 +2392,186 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>7.266954638779488</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Merangin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.1732797620287</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Merangin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>18.13372809662905</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Merangin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-4.821882742457076</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Merangin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6.757603687261877</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Merangin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.31731869699129</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Merangin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>4.302278867721125</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2000,7 +2588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2158,18 +2746,130 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>110.831039351955</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bungo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.481495420233796</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bungo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-8.82723776010128</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bungo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.866519215457007</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bungo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>2.226417824378659</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2186,7 +2886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2470,6 +3170,62 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1505</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Muaro Jambi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-18.86007358159301</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1505</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Muaro Jambi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-11.12345185493634</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2484,7 +3240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2572,6 +3328,118 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanjung Jabung Barat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.356881289340003</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanjung Jabung Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.72778215672144</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanjung Jabung Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1607031075964448</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanjung Jabung Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.836038771969059</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2586,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2786,6 +3654,34 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-3 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1508</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tebo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.347780106594069</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2800,7 +3696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2860,6 +3756,230 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarolangun</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8.345115414358961</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarolangun</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>18.26800169803232</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarolangun</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-10.44388310112588</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarolangun</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.120939821500017</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarolangun</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.893005208922427</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarolangun</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.597660546399068</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarolangun</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.172822523608137</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarolangun</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.3133292953839749</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2874,7 +3994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2965,6 +4085,62 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Batang Hari</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>15.80354718491168</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Batang Hari</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-10.71794470734582</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
